--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -17711,7 +17711,7 @@
         <v>1002</v>
       </c>
       <c r="B407" t="n">
-        <v>2.00674245319712</v>
+        <v>2.01577958439378</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="1004">
   <si>
     <t xml:space="preserve">Ref_Date</t>
   </si>
@@ -3017,6 +3017,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jan 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Value</t>
@@ -14446,6 +14449,17 @@
         <v>2.51</v>
       </c>
     </row>
+    <row r="795">
+      <c r="A795" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B795" t="n">
+        <v>1.77914110429449</v>
+      </c>
+      <c r="C795" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14463,7 +14477,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="2">
@@ -17708,10 +17722,10 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B407" t="n">
-        <v>2.01577958439378</v>
+        <v>2.0200498226409</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -5444,10 +5444,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>2.05524018205995</v>
+        <v>2.06540213826603</v>
       </c>
       <c r="C181" t="n">
-        <v>0.998897785704743</v>
+        <v>0.998890662838777</v>
       </c>
     </row>
     <row r="182">
@@ -5455,10 +5455,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>1.62555147780193</v>
+        <v>1.62682304205727</v>
       </c>
       <c r="C182" t="n">
-        <v>0.821740106957539</v>
+        <v>0.821722801049688</v>
       </c>
     </row>
     <row r="183">
@@ -5466,10 +5466,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>1.68493166096518</v>
+        <v>1.68590025012889</v>
       </c>
       <c r="C183" t="n">
-        <v>0.877084677047821</v>
+        <v>0.876469180629757</v>
       </c>
     </row>
     <row r="184">
@@ -5477,10 +5477,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>1.67550316392176</v>
+        <v>1.66796932284055</v>
       </c>
       <c r="C184" t="n">
-        <v>0.886374358173131</v>
+        <v>0.886964076767289</v>
       </c>
     </row>
     <row r="185">
@@ -5488,10 +5488,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>1.69227542590139</v>
+        <v>1.69810219114045</v>
       </c>
       <c r="C185" t="n">
-        <v>0.908432804322817</v>
+        <v>0.908469462648783</v>
       </c>
     </row>
     <row r="186">
@@ -5499,10 +5499,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>1.63895415898412</v>
+        <v>1.63929971780243</v>
       </c>
       <c r="C186" t="n">
-        <v>0.905803036435159</v>
+        <v>0.905913963486465</v>
       </c>
     </row>
     <row r="187">
@@ -5510,10 +5510,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>1.6251609065078</v>
+        <v>1.62704729429941</v>
       </c>
       <c r="C187" t="n">
-        <v>0.914842967608478</v>
+        <v>0.913969089901001</v>
       </c>
     </row>
     <row r="188">
@@ -5521,10 +5521,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>1.66680108231396</v>
+        <v>1.66011365832078</v>
       </c>
       <c r="C188" t="n">
-        <v>0.939288241050763</v>
+        <v>0.939930893218458</v>
       </c>
     </row>
     <row r="189">
@@ -5532,10 +5532,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>1.71628259868473</v>
+        <v>1.72135708752905</v>
       </c>
       <c r="C189" t="n">
-        <v>0.967951795221917</v>
+        <v>0.968112820566438</v>
       </c>
     </row>
     <row r="190">
@@ -5543,10 +5543,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>1.78687913113655</v>
+        <v>1.78669627351898</v>
       </c>
       <c r="C190" t="n">
-        <v>0.998757705756492</v>
+        <v>0.999013952423836</v>
       </c>
     </row>
     <row r="191">
@@ -5554,10 +5554,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>1.80543389132217</v>
+        <v>1.80825433495618</v>
       </c>
       <c r="C191" t="n">
-        <v>0.987970959573505</v>
+        <v>0.986682457370167</v>
       </c>
     </row>
     <row r="192">
@@ -5565,10 +5565,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>1.86195573088257</v>
+        <v>1.8540781778088</v>
       </c>
       <c r="C192" t="n">
-        <v>0.981126561580754</v>
+        <v>0.98193568308146</v>
       </c>
     </row>
     <row r="193">
@@ -5576,10 +5576,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>1.91491034820122</v>
+        <v>1.92093235952388</v>
       </c>
       <c r="C193" t="n">
-        <v>0.97576895006899</v>
+        <v>0.975977895383307</v>
       </c>
     </row>
     <row r="194">
@@ -5587,10 +5587,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>1.95268027854123</v>
+        <v>1.95192712237938</v>
       </c>
       <c r="C194" t="n">
-        <v>0.978597567975668</v>
+        <v>0.978951693665586</v>
       </c>
     </row>
     <row r="195">
@@ -5598,10 +5598,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>1.98033405202076</v>
+        <v>1.98449519344818</v>
       </c>
       <c r="C195" t="n">
-        <v>0.988793625623467</v>
+        <v>0.987255576357749</v>
       </c>
     </row>
     <row r="196">
@@ -5609,10 +5609,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>2.0015956945453</v>
+        <v>1.99241666747422</v>
       </c>
       <c r="C196" t="n">
-        <v>0.978228514309664</v>
+        <v>0.979243879303598</v>
       </c>
     </row>
     <row r="197">
@@ -5620,10 +5620,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>2.0620494393438</v>
+        <v>2.06871018511579</v>
       </c>
       <c r="C197" t="n">
-        <v>0.97810220388914</v>
+        <v>0.97838564913567</v>
       </c>
     </row>
     <row r="198">
@@ -5631,10 +5631,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>2.0532709733685</v>
+        <v>2.05234874357168</v>
       </c>
       <c r="C198" t="n">
-        <v>0.979425635948052</v>
+        <v>0.979806627547248</v>
       </c>
     </row>
     <row r="199">
@@ -5642,10 +5642,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>2.0450357450904</v>
+        <v>2.04960771037578</v>
       </c>
       <c r="C199" t="n">
-        <v>0.980057577948278</v>
+        <v>0.978349228641292</v>
       </c>
     </row>
     <row r="200">
@@ -5653,10 +5653,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>1.99394878433831</v>
+        <v>1.98505523838326</v>
       </c>
       <c r="C200" t="n">
-        <v>0.977197546857674</v>
+        <v>0.978102119366576</v>
       </c>
     </row>
     <row r="201">
@@ -5664,10 +5664,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>1.96584695066705</v>
+        <v>1.97151347891843</v>
       </c>
       <c r="C201" t="n">
-        <v>0.976101921647048</v>
+        <v>0.976525468954534</v>
       </c>
     </row>
     <row r="202">
@@ -5675,10 +5675,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>1.92888374343974</v>
+        <v>1.92832466024424</v>
       </c>
       <c r="C202" t="n">
-        <v>0.961540657435647</v>
+        <v>0.961881104384183</v>
       </c>
     </row>
     <row r="203">
@@ -5686,10 +5686,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>1.91568100189925</v>
+        <v>1.91949993591791</v>
       </c>
       <c r="C203" t="n">
-        <v>0.970041684429448</v>
+        <v>0.967997088457887</v>
       </c>
     </row>
     <row r="204">
@@ -5697,10 +5697,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>1.88837189835277</v>
+        <v>1.87805847666467</v>
       </c>
       <c r="C204" t="n">
-        <v>0.960559430397289</v>
+        <v>0.962647827067386</v>
       </c>
     </row>
   </sheetData>
@@ -17725,7 +17725,7 @@
         <v>1003</v>
       </c>
       <c r="B407" t="n">
-        <v>2.0200498226409</v>
+        <v>2.02131342064826</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -17725,7 +17725,7 @@
         <v>1003</v>
       </c>
       <c r="B407" t="n">
-        <v>2.02131342064826</v>
+        <v>2.02112788655055</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="1004">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="1005">
   <si>
     <t xml:space="preserve">Ref_Date</t>
   </si>
@@ -3026,6 +3026,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr 2026</t>
   </si>
 </sst>
 </file>
@@ -17728,6 +17731,14 @@
         <v>2.02112788655055</v>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B408" t="n">
+        <v>2.02062960833986</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -17736,7 +17736,7 @@
         <v>1004</v>
       </c>
       <c r="B408" t="n">
-        <v>2.02062960833986</v>
+        <v>2.01777196053827</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -3022,10 +3022,10 @@
     <t xml:space="preserve">Feb 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Mar 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mar 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Apr 2026</t>
@@ -14463,6 +14463,17 @@
         <v>2.42</v>
       </c>
     </row>
+    <row r="796">
+      <c r="A796" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B796" t="n">
+        <v>2.38532110091743</v>
+      </c>
+      <c r="C796" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14480,7 +14491,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="2">
@@ -17725,7 +17736,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B407" t="n">
         <v>2.02112788655055</v>
@@ -17736,7 +17747,7 @@
         <v>1004</v>
       </c>
       <c r="B408" t="n">
-        <v>2.01777196053827</v>
+        <v>2.01696350322923</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="1006">
   <si>
     <t xml:space="preserve">Ref_Date</t>
   </si>
@@ -3029,6 +3029,9 @@
   </si>
   <si>
     <t xml:space="preserve">Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 2026</t>
   </si>
 </sst>
 </file>
@@ -17747,7 +17750,15 @@
         <v>1004</v>
       </c>
       <c r="B408" t="n">
-        <v>2.01696350322923</v>
+        <v>2.01809217339207</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B409" t="n">
+        <v>2.04115053204294</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -3031,10 +3031,10 @@
     <t xml:space="preserve">Apr 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">May 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Jun 2026</t>
@@ -5632,10 +5632,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>2.05001271563122</v>
+        <v>2.01548946113031</v>
       </c>
       <c r="C197" t="n">
-        <v>0.97838564913567</v>
+        <v>0.978546880671824</v>
       </c>
     </row>
     <row r="198">
@@ -5643,10 +5643,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>2.05019192775109</v>
+        <v>2.00308848394088</v>
       </c>
       <c r="C198" t="n">
-        <v>0.979806627547248</v>
+        <v>0.98004755386932</v>
       </c>
     </row>
     <row r="199">
@@ -5654,10 +5654,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>2.05129147787246</v>
+        <v>2.00591988451422</v>
       </c>
       <c r="C199" t="n">
-        <v>0.978349228641292</v>
+        <v>0.978588167340797</v>
       </c>
     </row>
     <row r="200">
@@ -5665,10 +5665,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>2.0030844464957</v>
+        <v>1.98868278775084</v>
       </c>
       <c r="C200" t="n">
-        <v>0.978102119366576</v>
+        <v>0.978336558251256</v>
       </c>
     </row>
     <row r="201">
@@ -5676,10 +5676,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>1.95522333455888</v>
+        <v>1.95523440018676</v>
       </c>
       <c r="C201" t="n">
-        <v>0.97660179313361</v>
+        <v>0.976832956098968</v>
       </c>
     </row>
     <row r="202">
@@ -5687,10 +5687,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>1.92519620603387</v>
+        <v>1.92520159223443</v>
       </c>
       <c r="C202" t="n">
-        <v>0.961921842714499</v>
+        <v>0.962142512799314</v>
       </c>
     </row>
     <row r="203">
@@ -5701,7 +5701,7 @@
         <v>1.91959459777676</v>
       </c>
       <c r="C203" t="n">
-        <v>0.968225134182243</v>
+        <v>0.968432082199543</v>
       </c>
     </row>
     <row r="204">
@@ -5709,10 +5709,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>1.90051375401488</v>
+        <v>1.90052768326429</v>
       </c>
       <c r="C204" t="n">
-        <v>0.964423254978157</v>
+        <v>0.964938342788751</v>
       </c>
     </row>
     <row r="205">
@@ -5720,10 +5720,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>1.88728628320419</v>
+        <v>1.88932770951937</v>
       </c>
       <c r="C205" t="n">
-        <v>0.968073322337288</v>
+        <v>0.969734044261403</v>
       </c>
     </row>
   </sheetData>
@@ -14505,6 +14505,17 @@
         <v>2.96</v>
       </c>
     </row>
+    <row r="798">
+      <c r="A798" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B798" t="n">
+        <v>3.2258064516129</v>
+      </c>
+      <c r="C798" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14522,7 +14533,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="2">
@@ -17783,7 +17794,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B409" t="n">
         <v>2.03251702483921</v>
@@ -17794,7 +17805,7 @@
         <v>1007</v>
       </c>
       <c r="B410" t="n">
-        <v>2.04068273256804</v>
+        <v>2.02289187846786</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="1009">
   <si>
     <t xml:space="preserve">Ref_Date</t>
   </si>
@@ -3038,6 +3038,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -17805,7 +17808,15 @@
         <v>1007</v>
       </c>
       <c r="B410" t="n">
-        <v>2.02289187846786</v>
+        <v>2.0230089088786</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B411" t="n">
+        <v>2.03144426290031</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -17816,7 +17816,7 @@
         <v>1008</v>
       </c>
       <c r="B411" t="n">
-        <v>2.03144426290031</v>
+        <v>2.032132465996</v>
       </c>
     </row>
   </sheetData>

--- a/Data/C07 Figures.xlsx
+++ b/Data/C07 Figures.xlsx
@@ -3034,10 +3034,10 @@
     <t xml:space="preserve">May 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">Jun 2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jun 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Jul 2026</t>
@@ -5715,7 +5715,7 @@
         <v>1.90052768326429</v>
       </c>
       <c r="C204" t="n">
-        <v>0.964938342788751</v>
+        <v>0.964938059310884</v>
       </c>
     </row>
     <row r="205">
@@ -14519,6 +14519,17 @@
         <v>2.82</v>
       </c>
     </row>
+    <row r="799">
+      <c r="A799" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B799" t="n">
+        <v>2.79805352798053</v>
+      </c>
+      <c r="C799" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -14536,7 +14547,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="2">
@@ -17805,7 +17816,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B410" t="n">
         <v>2.0230089088786</v>
@@ -17816,7 +17827,7 @@
         <v>1008</v>
       </c>
       <c r="B411" t="n">
-        <v>2.032132465996</v>
+        <v>2.0353770189504</v>
       </c>
     </row>
   </sheetData>
